--- a/data/source_dossier.xlsx
+++ b/data/source_dossier.xlsx
@@ -1987,7 +1987,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Fig. A.1 technical-grade band 2.40–2.70 $/kg (US import unit value, CIF, 2025)</t>
+          <t>Fig. A.1 technical-grade band 2.43–2.55 $/kg (US import unit value of total hydrofluoric acid imports, CIF, 2025 quarters), shown as 2.4–2.6</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Total-row unit values span 2.43–2.55 $/kg in 2025 (2.47 for the year); the 2.70 upper end of the Fig. A.1 band is reached only at country level (e.g., Mexico, Q2 2025: 41,200/15,300 = 2.69 $/kg). State the basis of the band in the figure caption.</t>
+          <t>Total-row unit values span 2.43–2.55 $/kg in 2025 (2.47 for the year); the band was corrected from 2.4–2.7 on 2026-10-05.</t>
         </is>
       </c>
     </row>

--- a/data/source_dossier.xlsx
+++ b/data/source_dossier.xlsx
@@ -988,7 +988,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Business Society, 2025</t>
+          <t>Business Society, 2025b</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Kim, 2026</t>
+          <t>Kim, J.-U., 2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Reporter Kim Ji-hyun (distinct from 'Kim, 2026', the Dealsite article). 'Last year' = 2025; 'this month' = April 2026.</t>
+          <t>Reporter Kim Ji-hyun (distinct from 'Kim, J.-U., 2026', the Dealsite article). 'Last year' = 2025; 'this month' = April 2026.</t>
         </is>
       </c>
     </row>
@@ -2138,47 +2138,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>生意社：2024年氢氟酸行情回顾及2025年的展望</t>
+          <t>生意社：2025年萤石行情下滑 2026年将弱势复苏</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Review of the 2024 hydrofluoric acid market and outlook for 2025</t>
+          <t>Fluorspar prices fell in 2025 and are expected to recover weakly in 2026</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.100ppi.com/forecast/detail-20250113-197484.html</t>
+          <t>https://finance.sina.com.cn/money/future/nyzx/2025-12-30/doc-inheqixr5797475.shtml</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Paragraph on raw-material fluorspar (published 2025-01-13)</t>
+          <t>Paragraph on the 2025 fluorspar market (Business Society via Sina Finance, published 2025-12-30)</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Fluorspar average price 3,531.25 CNY/t (start of 2024) and 3,622.5 CNY/t (end of 2024); 3,622.5 used as the 2025 start-of-year value</t>
+          <t>Fluorspar average price 3,622.5 CNY/t (start of 2025) and 3,400 CNY/t (end of 2025); 3,622.5 used as the upper bound of the fluorspar price range</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>在2024年，萤石价格呈现小幅上涨趋势，年初平均价格为3531.25元/吨，年底均价为3622.5元/吨，涨幅2.58%。</t>
+          <t>2025年国内萤石价格走势下滑，年初平均价格为3622.5元/吨，年底萤石均价为3400元/吨，全年跌幅为6.14%。</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>In 2024, fluorspar prices rose slightly: the average price was 3,531.25 CNY/t at the start of the year and 3,622.5 CNY/t at the end of the year, an increase of 2.58%.</t>
+          <t>Domestic fluorspar prices fell in 2025: the average price was 3,622.5 CNY/t at the start of the year and 3,400 CNY/t at the end of the year, a decrease of 6.14% over the year.</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>excerpt verified 2026-10-05</t>
+          <t>excerpt verified 2026-10-12</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>The source gives 3,622.5 CNY/t as the end-of-2024 average, not a 2025 value; using it as the 2025 start-of-year price is an interpretation. The page sits behind a browser check; text read after passing the check. If cited alongside 'Business Society, 2025' (rawmex), use 2025a/2025b.</t>
+          <t>Replaces the earlier entry (Business Society review of the 2024 market, 100ppi.com, 2025-01-13), which reports the same 3,622.5 CNY/t as the end-of-2024 average.</t>
         </is>
       </c>
     </row>

--- a/data/source_dossier.xlsx
+++ b/data/source_dossier.xlsx
@@ -728,32 +728,32 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>§3.3.4 (p. 16, PDF p. 21); Table 3.3-6 (PDF p. 17); Tables 3.4-1 and 3.5-1 (PDF pp. 21–22); Table 3.3-2 (product standard Q/KAISN 04-2018); §3.6 (process description)</t>
+          <t>§3.3.4 (p. 16, PDF p. 21); Table 3.3-6 (PDF p. 17); Tables 3.4-1 and 3.5-1 (PDF pp. 21–22); Table 3.3-2 (product standard Q/KAISN 04-2018); §3.6 (process description); Table 3.4-1 (PDF p. 21) for the co-products</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>New 18 kt/yr ppt-grade (49–50%) line: actual total investment 238.66 million CNY; 30 new staff; 7,200 h/yr; electricity 7,254,000 kWh/yr; steam 6,300 t/yr; AHF feed 12,348 t/yr; grade specifications EL to UP-SSS; F2/N2 oxidative pretreatment</t>
+          <t>New 18 kt/yr ppt-grade (49–50%) line: actual total investment 238.66 million CNY; 30 new staff; 7,200 h/yr; electricity 7,254,000 kWh/yr; steam 6,300 t/yr; AHF feed 12,348 t/yr; grade specifications EL to UP-SSS; F2/N2 oxidative pretreatment; co-products listed as a check only: high-purity AHF 100 t/yr, industrial-grade hydrofluoric acid 3,500 t/yr, industrial-grade AHF 1,500 t/yr</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>项目实际总投资23866万元。项目新增定员30人，新增人数主要为新建纯化装置的操作工人或技术人员。 | 表3.3-6: 新增用电量7254000 kWh/a；新增用汽量6300t/a | 表3.5-1: 无水氟化氢 99.99% 1.544 12348.00</t>
+          <t>项目实际总投资23866万元。项目新增定员30人，新增人数主要为新建纯化装置的操作工人或技术人员。 | 表3.3-6: 新增用电量7254000 kWh/a；新增用汽量6300t/a | 表3.5-1: 无水氟化氢 99.99% 1.544 12348.00 | 表3.4-1: 电子级氢氟酸 18000t/a | 高纯无水氟化氢（联产产品）100 | 工业级氢氟酸（联产产品）3500 | 工业级无水氟化氢（联产产品）1500</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>The actual total investment of the project was 238.66 million CNY. The project adds 30 staff, mainly operators or technicians for the new purification unit. | Table 3.3-6: additional electricity use 7,254,000 kWh/yr; additional steam use 6,300 t/yr | Table 3.5-1: anhydrous hydrogen fluoride, 99.99%, 1.544 t/h, 12,348.00 t/yr</t>
+          <t>The actual total investment of the project was 238.66 million CNY. The project adds 30 staff, mainly operators or technicians for the new purification unit. | Table 3.3-6: additional electricity use 7,254,000 kWh/yr; additional steam use 6,300 t/yr | Table 3.5-1: anhydrous hydrogen fluoride, 99.99%, 1.544 t/h, 12,348.00 t/yr | Table 3.4-1: electronic-grade hydrofluoric acid 18,000 t/yr | high-purity anhydrous hydrogen fluoride (co-product) 100 | industrial-grade hydrofluoric acid (co-product) 3,500 | industrial-grade anhydrous hydrogen fluoride (co-product) 1,500</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>excerpt verified 2026-10-05</t>
+          <t>excerpt verified 2026-10-05; Table 3.4-1 verified 2026-10-23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Verified against the local copy (data_v2/raw/kaisheng.pdf). The planned investment was 23,896.11 ×10^4 CNY; the actual 23,866 ×10^4 CNY is used.</t>
+          <t>Verified against the local copy (data_v2/raw/kaisheng.pdf). The planned investment was 23,896.11 ×10^4 CNY; the actual 23,866 ×10^4 CNY is used. The co-products in Table 3.4-1 sum to about 5,100 t/yr of product mass, with the industrial-grade acid counted as solution. The model uses the HF mass balance instead: 12,348 t/yr of AHF less 8,910 t/yr of HF in the electronic-grade product (18,000 t/yr at 49.5% HF) leaves 3,438 t/yr of HF, or 0.39 t per t of product (SI Table S6, M6). The two agree if the industrial-grade acid contains about 53% HF ((3,438 − 1,600)/3,500).</t>
         </is>
       </c>
     </row>
